--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFC3D3A0-C629-465F-ADA8-05944F026092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C41199B9-B922-413F-AFC7-7CAA2B53ED1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="3800" windowWidth="28540" windowHeight="17000" xr2:uid="{2CF25DFD-8DF8-4386-923B-89995E343796}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{7C3F422F-8801-460A-B63E-36CCC13C52AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Designator</t>
   </si>
@@ -51,13 +51,25 @@
     <t>Footprint</t>
   </si>
   <si>
-    <t>C1, C2, C3</t>
+    <t>C1, C3_IMU1, C3_IMU2, C3_IMU3, C3_IMU4</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>Capacitor 0201</t>
+  </si>
+  <si>
+    <t>C2_IMU1, C2_IMU2, C2_IMU3, C2_IMU4</t>
   </si>
   <si>
     <t>1uF</t>
   </si>
   <si>
-    <t>Capacitor 0402</t>
+    <t>C4_IMU1, C4_IMU2, C4_IMU3, C4_IMU4</t>
+  </si>
+  <si>
+    <t>2.2uF</t>
   </si>
   <si>
     <t>J1</t>
@@ -67,6 +79,21 @@
   </si>
   <si>
     <t>U1</t>
+  </si>
+  <si>
+    <t>24AA32AT-I/MC</t>
+  </si>
+  <si>
+    <t>TDFN-8 2x3mm</t>
+  </si>
+  <si>
+    <t>U2_IMU1, U2_IMU2, U2_IMU3, U2_IMU4</t>
+  </si>
+  <si>
+    <t>ICM-42670-P</t>
+  </si>
+  <si>
+    <t>U3_IMU1, U3_IMU2, U3_IMU3, U3_IMU4</t>
   </si>
   <si>
     <t>SK6805-EC15</t>
@@ -445,17 +472,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2C7A470-6701-4D7A-A375-54627C11C94D}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C1B36E-CF9D-4D98-9280-2630D1DF6823}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="87.81640625" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" customWidth="1"/>
-    <col min="3" max="3" width="25.36328125" customWidth="1"/>
-    <col min="4" max="4" width="25.08984375" customWidth="1"/>
+    <col min="1" max="1" width="86.53125" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="3" max="3" width="24.9296875" customWidth="1"/>
+    <col min="4" max="4" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -469,12 +496,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -483,36 +510,92 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="120" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C41199B9-B922-413F-AFC7-7CAA2B53ED1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C7A7EC0-C19B-4AB1-B4F7-0719E71A6CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{7C3F422F-8801-460A-B63E-36CCC13C52AA}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{B5BB6934-F8DB-46C5-A143-CE09B9DB759D}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9C1B36E-CF9D-4D98-9280-2630D1DF6823}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB07E2B-DBA6-4AF3-9F63-0D008D09A332}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>

--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C7A7EC0-C19B-4AB1-B4F7-0719E71A6CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86AE2E9C-9FA7-4964-9B59-EB8DD525C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{B5BB6934-F8DB-46C5-A143-CE09B9DB759D}"/>
+    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="15360" xr2:uid="{4ED6EE7B-77BE-4251-A9B3-7832B2B925AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -472,17 +472,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB07E2B-DBA6-4AF3-9F63-0D008D09A332}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CEE52FA-CDE2-4BC9-8C86-C8CC9542CF83}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="86.53125" customWidth="1"/>
-    <col min="2" max="2" width="10.9296875" customWidth="1"/>
-    <col min="3" max="3" width="24.9296875" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="1" max="1" width="87.81640625" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="25.36328125" customWidth="1"/>
+    <col min="4" max="4" width="25.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -496,7 +496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -510,7 +510,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -524,7 +524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -552,7 +552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -566,7 +566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -580,7 +580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>

--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86AE2E9C-9FA7-4964-9B59-EB8DD525C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81CB0AE3-D187-4942-A86A-AEEA76D5F26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="15360" xr2:uid="{4ED6EE7B-77BE-4251-A9B3-7832B2B925AD}"/>
+    <workbookView xWindow="530" yWindow="1760" windowWidth="23190" windowHeight="17120" xr2:uid="{75FB7E1C-F937-4BDF-9632-EF7E586B1CBE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CEE52FA-CDE2-4BC9-8C86-C8CC9542CF83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539FAB7A-7DDF-4B01-BB99-6D248365B40D}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81CB0AE3-D187-4942-A86A-AEEA76D5F26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C3BAD16-2048-4707-A943-2AC6778D562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="530" yWindow="1760" windowWidth="23190" windowHeight="17120" xr2:uid="{75FB7E1C-F937-4BDF-9632-EF7E586B1CBE}"/>
+    <workbookView xWindow="530" yWindow="1760" windowWidth="23190" windowHeight="17120" xr2:uid="{16B48E31-9BAB-498D-8CEB-020C7A012280}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539FAB7A-7DDF-4B01-BB99-6D248365B40D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CE3813-6A3C-4590-B368-5381AA65B784}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C3BAD16-2048-4707-A943-2AC6778D562F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B76F3CB-7D11-470F-8F75-C45F4D1A9DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="530" yWindow="1760" windowWidth="23190" windowHeight="17120" xr2:uid="{16B48E31-9BAB-498D-8CEB-020C7A012280}"/>
+    <workbookView xWindow="530" yWindow="1760" windowWidth="23190" windowHeight="17120" xr2:uid="{7500B7DB-937E-4DDB-9AF7-7FFAD8991734}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57CE3813-6A3C-4590-B368-5381AA65B784}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B54E7C6-BF6D-4188-AD67-964261307A9C}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA98016D-47D9-4C4B-AC9E-97C1457337C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B806ED89-4911-4473-9273-F117D20FEE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="6860" windowWidth="15000" windowHeight="13120" xr2:uid="{EFA6C76A-39D2-4FE3-831F-DCCA47028000}"/>
+    <workbookView xWindow="-21770" yWindow="1560" windowWidth="18860" windowHeight="19610" xr2:uid="{278795C2-0BCF-4011-8428-C405520AE823}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ACF4BA5-7843-4C03-A2B4-B70F7065C2DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA875165-BB01-457B-9EEF-D39AC722445C}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B806ED89-4911-4473-9273-F117D20FEE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD9E479D-7542-498B-B890-57EE562E53C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21770" yWindow="1560" windowWidth="18860" windowHeight="19610" xr2:uid="{278795C2-0BCF-4011-8428-C405520AE823}"/>
+    <workbookView xWindow="-34450" yWindow="340" windowWidth="24080" windowHeight="21020" xr2:uid="{01E0ED95-4AD8-4EAB-BBFA-F04147F704DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Comment</t>
+    <t>Name</t>
   </si>
   <si>
     <t>Footprint</t>
@@ -99,7 +99,7 @@
     <t>U2_CH1, U2_CH2, U2_CH3, U2_CH4</t>
   </si>
   <si>
-    <t>ICM-42688-P</t>
+    <t>ICM-45686</t>
   </si>
   <si>
     <t>U3_CH1, U3_CH2, U3_CH3, U3_CH4</t>
@@ -481,7 +481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA875165-BB01-457B-9EEF-D39AC722445C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8964C761-7A5F-49D0-88A8-035FCF3D2A9E}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>

--- a/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
+++ b/Project Outputs for Twintig-IMUs/BOM/Bill of Materials-Twintig-IMUs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFiles\x-io\Services\MICA Lab\Twintig\Twintig-IMUs\Project Outputs for Twintig-IMUs\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD9E479D-7542-498B-B890-57EE562E53C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9B0EA99-6E6B-41CD-9852-9A314C528529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34450" yWindow="340" windowWidth="24080" windowHeight="21020" xr2:uid="{01E0ED95-4AD8-4EAB-BBFA-F04147F704DE}"/>
+    <workbookView xWindow="-34370" yWindow="620" windowWidth="33640" windowHeight="20650" xr2:uid="{85CEBEF7-6ADA-410C-8F3A-2F95F15A842A}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-Twintig-IMUs" sheetId="1" r:id="rId1"/>
@@ -481,7 +481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8964C761-7A5F-49D0-88A8-035FCF3D2A9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43407BEA-79C4-4ED5-8A66-7777712D0744}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
